--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Procedure: Outpatient, ResourceType Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA V CPT (file 9000010.18) to FHIR Procedure</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -608,6 +608,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-24:1539: fixed value "completed" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -808,6 +812,10 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-23:1314: fixed value "371883000" {null}</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
@@ -942,10 +950,10 @@
     <t>Procedure.code.text</t>
   </si>
   <si>
+    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
+  </si>
+  <si>
     <t>Dim.ProviderNarrative.ProviderNarrative</t>
-  </si>
-  <si>
-    <t>1301: source value from V CPT - PROVIDER NARRATIVE &gt; PROVIDER NARRATIVE - NARRATIVE (#9000010.18-.04 &gt; 9999999.27-.01)</t>
   </si>
   <si>
     <t>Procedure.subject</t>
@@ -1006,6 +1014,9 @@
   </si>
   <si>
     <t>PV1-19</t>
+  </si>
+  <si>
+    <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.VisitDateTime
@@ -1016,9 +1027,6 @@
 Outpat.WorkloadVProcedureDiagnosis.VisitDateTime</t>
   </si>
   <si>
-    <t>1300: reference from V CPT - VISIT (#9000010.18-.03)</t>
-  </si>
-  <si>
     <t>Procedure.performed[x]</t>
   </si>
   <si>
@@ -1059,6 +1067,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>1310: source value from V CPT - EVENT DATE AND TIME (#9000010.18-1201)</t>
   </si>
   <si>
     <t>Outpat.VProcedure.EventDateTime
@@ -1067,9 +1078,6 @@
 Outpat.WorkloadVProcedureDiagnosis.EventDateTime</t>
   </si>
   <si>
-    <t>1310: source value from V CPT - EVENT DATE AND TIME (#9000010.18-1201)</t>
-  </si>
-  <si>
     <t>Procedure.recorder</t>
   </si>
   <si>
@@ -1498,11 +1506,11 @@
     <t>Act.text</t>
   </si>
   <si>
+    <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
+  </si>
+  <si>
     <t>Outpat.VProcedure.Comments
 Outpat.WorkloadVProcedure.Comments</t>
-  </si>
-  <si>
-    <t>1312: source value from V CPT - COMMENTS (#9000010.18-81101)</t>
   </si>
   <si>
     <t>Procedure.focalDevice</t>
@@ -1957,8 +1965,8 @@
     <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="51.578125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="122.95703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="122.95703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="51.578125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3864,37 +3872,37 @@
         <v>188</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3913,16 +3921,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3948,13 +3956,13 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3972,7 +3980,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3987,10 +3995,10 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -4007,10 +4015,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4033,13 +4041,13 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4066,13 +4074,13 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>79</v>
@@ -4090,7 +4098,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4108,10 +4116,10 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4125,10 +4133,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4151,13 +4159,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4208,7 +4216,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4226,7 +4234,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4243,10 +4251,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4275,7 +4283,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>138</v>
@@ -4316,19 +4324,19 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4346,7 +4354,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -4363,10 +4371,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4389,19 +4397,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4450,7 +4458,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4468,13 +4476,13 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4485,10 +4493,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4511,13 +4519,13 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4568,7 +4576,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4586,7 +4594,7 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4603,10 +4611,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4635,7 +4643,7 @@
         <v>136</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>138</v>
@@ -4676,19 +4684,19 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4706,7 +4714,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
@@ -4723,10 +4731,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4752,16 +4760,16 @@
         <v>103</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4810,7 +4818,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4828,13 +4836,13 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4845,10 +4853,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4871,16 +4879,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4930,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4948,13 +4956,13 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4965,10 +4973,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4994,14 +5002,14 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5050,7 +5058,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5062,33 +5070,33 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>255</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5111,17 +5119,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5170,7 +5178,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5188,13 +5196,13 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5205,10 +5213,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5231,19 +5239,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5292,7 +5300,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5310,13 +5318,13 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5327,10 +5335,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5353,19 +5361,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5414,7 +5422,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5432,13 +5440,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5449,14 +5457,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5475,17 +5483,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5510,13 +5518,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5534,7 +5542,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5549,16 +5557,16 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5569,10 +5577,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5595,13 +5603,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5652,7 +5660,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5670,7 +5678,7 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
@@ -5687,10 +5695,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5719,7 +5727,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5760,19 +5768,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5790,7 +5798,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5807,10 +5815,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5833,19 +5841,19 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5894,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5912,27 +5920,27 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5955,19 +5963,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6016,7 +6024,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6034,31 +6042,31 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6077,13 +6085,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6134,7 +6142,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6149,30 +6157,30 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>309</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6195,16 +6203,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6254,7 +6262,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6269,30 +6277,30 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6315,16 +6323,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6362,17 +6370,17 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6387,16 +6395,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6407,13 +6415,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>79</v>
@@ -6435,16 +6443,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6494,7 +6502,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6509,30 +6517,30 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6555,13 +6563,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6612,7 +6620,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6630,10 +6638,10 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6647,10 +6655,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6673,13 +6681,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6730,7 +6738,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6748,10 +6756,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6765,10 +6773,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6791,13 +6799,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6848,7 +6856,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6863,10 +6871,10 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6883,10 +6891,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6909,13 +6917,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6966,7 +6974,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6984,7 +6992,7 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
@@ -7001,10 +7009,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7033,7 +7041,7 @@
         <v>136</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>138</v>
@@ -7086,7 +7094,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7104,7 +7112,7 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
@@ -7121,14 +7129,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7150,10 +7158,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>138</v>
@@ -7208,7 +7216,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7243,10 +7251,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7269,17 +7277,17 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7304,13 +7312,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7328,7 +7336,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7343,16 +7351,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7363,10 +7371,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7389,17 +7397,17 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7448,7 +7456,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>89</v>
@@ -7463,30 +7471,30 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7509,17 +7517,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7568,7 +7576,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7586,7 +7594,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7603,10 +7611,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7629,17 +7637,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7688,7 +7696,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7706,10 +7714,10 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7723,10 +7731,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7749,16 +7757,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7784,13 +7792,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7808,7 +7816,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7823,30 +7831,30 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7869,16 +7877,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7928,7 +7936,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7943,13 +7951,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>79</v>
@@ -7963,10 +7971,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7989,16 +7997,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8024,13 +8032,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8048,7 +8056,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8066,13 +8074,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8083,10 +8091,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8109,16 +8117,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8144,13 +8152,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8168,7 +8176,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8186,7 +8194,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8203,10 +8211,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8229,16 +8237,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8288,7 +8296,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8306,7 +8314,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8323,10 +8331,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8349,16 +8357,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8384,13 +8392,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8408,7 +8416,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8426,7 +8434,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8443,10 +8451,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8469,17 +8477,17 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8528,7 +8536,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8546,7 +8554,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8563,10 +8571,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8589,13 +8597,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8622,13 +8630,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8646,7 +8654,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8664,7 +8672,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8681,10 +8689,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8707,13 +8715,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8764,7 +8772,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8779,16 +8787,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8799,10 +8807,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8825,13 +8833,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8882,7 +8890,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8900,7 +8908,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8917,10 +8925,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8949,7 +8957,7 @@
         <v>136</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>138</v>
@@ -8990,19 +8998,19 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9020,7 +9028,7 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -9037,10 +9045,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9063,16 +9071,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9122,7 +9130,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9140,7 +9148,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9157,10 +9165,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9183,13 +9191,13 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9240,7 +9248,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9258,7 +9266,7 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9275,10 +9283,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9301,13 +9309,13 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9358,7 +9366,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>89</v>
@@ -9376,7 +9384,7 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
@@ -9385,18 +9393,18 @@
         <v>132</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9419,13 +9427,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9476,7 +9484,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9494,7 +9502,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9511,10 +9519,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9537,13 +9545,13 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9594,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9612,7 +9620,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9629,10 +9637,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9661,7 +9669,7 @@
         <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -9714,7 +9722,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9732,7 +9740,7 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9749,14 +9757,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9778,10 +9786,10 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>138</v>
@@ -9836,7 +9844,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9871,10 +9879,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9897,13 +9905,13 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9933,10 +9941,10 @@
         <v>113</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9954,7 +9962,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9972,7 +9980,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9989,10 +9997,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10015,13 +10023,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10072,7 +10080,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>89</v>
@@ -10090,7 +10098,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10107,10 +10115,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10133,19 +10141,19 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10194,7 +10202,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10212,7 +10220,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -10229,10 +10237,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10255,16 +10263,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10290,13 +10298,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10314,7 +10322,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10332,7 +10340,7 @@
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-24:1539: fixed value "completed" {null}</t>
+inv-30:1539: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -813,7 +813,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-23:1314: fixed value "371883000" {null}</t>
+inv-29:1314: fixed value = 371883000 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-30:1539: fixed value = completed {null}</t>
+inv-28:1539: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -813,7 +813,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1314: fixed value = 371883000 {null}</t>
+inv-27:1314: fixed value = 371883000 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-28:1539: fixed value = completed {null}</t>
+inv-30:1539: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -813,7 +813,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-27:1314: fixed value = 371883000 {null}</t>
+inv-29:1314: fixed value = 371883000 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-30:1539: fixed value = completed {null}</t>
+inv-31:1539: fixed value = completed {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -813,7 +813,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-29:1314: fixed value = 371883000 {null}</t>
+inv-30:1314: fixed value = 371883000 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureOutpatientProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA V CPT (file 9000010.18) to FHIR Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file V CPT (#9000010.18) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
